--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486452_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486452_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>D. SARAIVA SEIXAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0857</v>
+        <v>4.6219</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6001</v>
+        <v>1.7313</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4856</v>
+        <v>2.8906</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7524999999999999</v>
+        <v>1.1897</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1644</v>
+        <v>0.6965</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5881</v>
+        <v>0.4933</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7398</v>
+        <v>0.3165</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6633</v>
+        <v>1.0799</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0765</v>
+        <v>-0.7634</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0127</v>
+        <v>0.8732</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4989</v>
+        <v>-0.3834</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5116000000000001</v>
+        <v>1.2566</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1157</v>
+        <v>0.7796</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3828</v>
+        <v>0.2848</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7329</v>
+        <v>0.4948</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. SARAIVA SEIXAS</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.087</v>
+        <v>4.155</v>
       </c>
       <c r="E3" t="n">
-        <v>1.104</v>
+        <v>1.7002</v>
       </c>
       <c r="F3" t="n">
-        <v>2.983</v>
+        <v>2.4548</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1897</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6965</v>
+        <v>0.1644</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4933</v>
+        <v>0.5881</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3165</v>
+        <v>0.7398</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0799</v>
+        <v>0.6633</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7634</v>
+        <v>0.0765</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8732</v>
+        <v>0.0127</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3834</v>
+        <v>-0.4989</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2566</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2448</v>
+        <v>2.185</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3425</v>
+        <v>1.4829</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5873</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5993</v>
+        <v>4.1118</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5298</v>
+        <v>1.6416</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0695</v>
+        <v>2.4702</v>
       </c>
       <c r="G4" t="n">
         <v>1.5327</v>
@@ -766,13 +766,13 @@
         <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0242</v>
+        <v>1.5367</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8736</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1506</v>
+        <v>0.5513</v>
       </c>
       <c r="V4" t="n">
         <v>1.695</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2141</v>
+        <v>2.4637</v>
       </c>
       <c r="E5" t="n">
-        <v>2.507</v>
+        <v>2.9107</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2929</v>
+        <v>-0.447</v>
       </c>
       <c r="G5" t="n">
         <v>0.5551</v>
@@ -844,13 +844,13 @@
         <v>0.2175</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0583</v>
+        <v>0.1914</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.411</v>
+        <v>-0.0072</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3527</v>
+        <v>0.1986</v>
       </c>
       <c r="V5" t="n">
         <v>1.4997</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7451</v>
+        <v>2.3647</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3571</v>
+        <v>1.7609</v>
       </c>
       <c r="F6" t="n">
-        <v>0.388</v>
+        <v>0.6038</v>
       </c>
       <c r="G6" t="n">
         <v>0.8746</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2604</v>
+        <v>0.8799</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1971</v>
+        <v>0.6009</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0633</v>
+        <v>0.2791</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0435</v>
+        <v>0.7652</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1887</v>
+        <v>-0.3437</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2321</v>
+        <v>1.1088</v>
       </c>
       <c r="G7" t="n">
         <v>2.2171</v>
@@ -1000,13 +1000,13 @@
         <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.6345</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5997</v>
+        <v>0.4446</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3131</v>
+        <v>0.1899</v>
       </c>
       <c r="V7" t="n">
         <v>-3.174</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5674</v>
+        <v>0.2215</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.047</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4796</v>
+        <v>0.1283</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5088</v>
+        <v>-0.1226</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.1232</v>
+        <v>0.079</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6143999999999999</v>
+        <v>-0.2016</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.5191</v>
+        <v>0.0322</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.5573</v>
+        <v>1.0434</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0382</v>
+        <v>-1.0112</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0102</v>
+        <v>-0.1548</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5659</v>
+        <v>-0.9643</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.8096</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.2626</v>
+        <v>0.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1393</v>
+        <v>-0.1562</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4322</v>
+        <v>-0.1766</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7071</v>
+        <v>0.0204</v>
       </c>
       <c r="V8" t="n">
-        <v>2.0647</v>
+        <v>-0.3698</v>
       </c>
       <c r="W8" t="n">
-        <v>3.3899</v>
+        <v>1.3252</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3252</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5885</v>
+        <v>-0.9969</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7218</v>
+        <v>-1.9453</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1334</v>
+        <v>0.9484</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2872</v>
@@ -1156,13 +1156,13 @@
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6542</v>
+        <v>0.2457</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1971</v>
+        <v>-0.0264</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4571</v>
+        <v>0.2722</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9554</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0677</v>
+        <v>-1.0776</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-4.9585</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2416</v>
+        <v>3.8809</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1226</v>
+        <v>0.3076</v>
       </c>
       <c r="H10" t="n">
-        <v>0.079</v>
+        <v>0.082</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2016</v>
+        <v>0.2255</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0322</v>
+        <v>-0.8589</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0434</v>
+        <v>0.1523</v>
       </c>
       <c r="L10" t="n">
         <v>-1.0112</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1548</v>
+        <v>1.1664</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9643</v>
+        <v>-0.0703</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8096</v>
+        <v>1.2367</v>
       </c>
       <c r="P10" t="n">
-        <v>0.87</v>
+        <v>-3.4801</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-6.5252</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9576</v>
+        <v>3.0451</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4454</v>
+        <v>1.1602</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0959</v>
+        <v>0.7306</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3495</v>
+        <v>0.4296</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3698</v>
+        <v>0.9347</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3252</v>
+        <v>1.695</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.695</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0016</v>
+        <v>-1.3715</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6975</v>
+        <v>-4.2777</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6959</v>
+        <v>2.9061</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3076</v>
+        <v>-1.5184</v>
       </c>
       <c r="H11" t="n">
-        <v>0.082</v>
+        <v>-1.1741</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2255</v>
+        <v>-0.3442</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8589</v>
+        <v>-1.4122</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1523</v>
+        <v>0.0397</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0112</v>
+        <v>-1.4519</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1664</v>
+        <v>-0.1062</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0703</v>
+        <v>-1.2138</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2367</v>
+        <v>1.1076</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.4801</v>
+        <v>-0.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.5252</v>
+        <v>-3.2626</v>
       </c>
       <c r="R11" t="n">
-        <v>3.0451</v>
+        <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2362</v>
+        <v>0.8217</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.2019</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2447</v>
+        <v>0.6198</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9347</v>
+        <v>0.1952</v>
       </c>
       <c r="W11" t="n">
-        <v>1.695</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5769</v>
+        <v>-2.6</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5755</v>
+        <v>-2.5864</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9986</v>
+        <v>-0.0135</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5184</v>
+        <v>-2.5088</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1741</v>
+        <v>-3.1232</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3442</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4122</v>
+        <v>-2.5191</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0397</v>
+        <v>-2.5573</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4519</v>
+        <v>0.0382</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1062</v>
+        <v>0.0102</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2138</v>
+        <v>-0.5659</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1076</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.87</v>
+        <v>-3.2626</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.2626</v>
+        <v>-4.3501</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3837</v>
+        <v>1.1068</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0959</v>
+        <v>0.8929</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.2139</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1952</v>
+        <v>2.0647</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1952</v>
+        <v>3.3899</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.9726</v>
+        <v>12.6578</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9586</v>
+        <v>-4.2737</v>
       </c>
       <c r="F13" t="n">
-        <v>16.9312</v>
+        <v>16.9314</v>
       </c>
       <c r="G13" t="n">
         <v>2.9923</v>
@@ -1441,22 +1441,22 @@
         <v>6.3829</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1570000000000007</v>
+        <v>0.1570000000000005</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6832</v>
+        <v>3.683200000000001</v>
       </c>
       <c r="L13" t="n">
         <v>-3.5262</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8352</v>
+        <v>2.835200000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.073499999999999</v>
+        <v>-7.0735</v>
       </c>
       <c r="O13" t="n">
-        <v>9.908899999999999</v>
+        <v>9.908900000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-2.1751</v>
@@ -1468,13 +1468,13 @@
         <v>19.5757</v>
       </c>
       <c r="S13" t="n">
-        <v>8.700200000000001</v>
+        <v>9.385299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>4.7288</v>
+        <v>5.4138</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9715</v>
+        <v>3.9717</v>
       </c>
       <c r="V13" t="n">
         <v>2.455099999999999</v>
@@ -1483,13 +1483,13 @@
         <v>11.9061</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.450999999999999</v>
+        <v>-9.451000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. BOMBINO PARADA</t>
+          <t>O. MATULIONIS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6711</v>
+        <v>3.2836</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3241</v>
+        <v>0.8042</v>
       </c>
       <c r="F14" t="n">
-        <v>1.347</v>
+        <v>2.4794</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6949</v>
+        <v>2.1093</v>
       </c>
       <c r="H14" t="n">
-        <v>1.004</v>
+        <v>1.8216</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6909</v>
+        <v>0.2877</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8466</v>
+        <v>1.5549</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7318</v>
+        <v>1.9923</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1147</v>
+        <v>-0.4374</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1517</v>
+        <v>0.5544</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7278</v>
+        <v>-0.1707</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.7251</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R14" t="n">
-        <v>3.4801</v>
+        <v>3.2626</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2413</v>
+        <v>-1.153</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3497</v>
+        <v>-0.5756</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.591</v>
+        <v>-0.5774</v>
       </c>
       <c r="V14" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.13</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.5204</v>
-      </c>
       <c r="X14" t="n">
-        <v>-0.3904</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. MATULIONIS</t>
+          <t>P. BOMBINO PARADA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2104</v>
+        <v>3.0622</v>
       </c>
       <c r="E15" t="n">
-        <v>0.916</v>
+        <v>1.6536</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2944</v>
+        <v>1.4086</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1093</v>
+        <v>1.6949</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8216</v>
+        <v>1.004</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2877</v>
+        <v>0.6909</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5549</v>
+        <v>2.8466</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9923</v>
+        <v>2.7318</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4374</v>
+        <v>0.1147</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5544</v>
+        <v>-1.1517</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1707</v>
+        <v>-1.7278</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7251</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R15" t="n">
-        <v>3.2626</v>
+        <v>3.4801</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2262</v>
+        <v>-0.8502</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4638</v>
+        <v>-0.3208</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7624</v>
+        <v>-0.5294</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3698</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.5204</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7602</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4797</v>
+        <v>2.1484</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5763</v>
+        <v>0.7998</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9034</v>
+        <v>1.3486</v>
       </c>
       <c r="G16" t="n">
         <v>-0.08210000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>2.8276</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8085</v>
+        <v>-1.1398</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0719</v>
+        <v>-0.8484</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2634</v>
+        <v>-0.2914</v>
       </c>
       <c r="V16" t="n">
         <v>0.7602</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.2254</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3755</v>
+        <v>-0.7721</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4687</v>
+        <v>0.5467</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2201</v>
+        <v>0.8529</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0066</v>
+        <v>0.7238</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2136</v>
+        <v>0.1291</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3285</v>
+        <v>-0.2674</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3285</v>
+        <v>-0.2674</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8915999999999999</v>
+        <v>1.1203</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6781</v>
+        <v>0.9912</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2136</v>
+        <v>0.1291</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0035</v>
+        <v>-0.6009</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6886</v>
+        <v>-0.2872</v>
       </c>
       <c r="U17" t="n">
-        <v>0.315</v>
+        <v>-0.3137</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0906</v>
+        <v>-0.6313</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8839</v>
+        <v>-1.8225</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7933</v>
+        <v>1.1913</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8529</v>
+        <v>1.2201</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7238</v>
+        <v>1.0066</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1291</v>
+        <v>0.2136</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2674</v>
+        <v>0.3285</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2674</v>
+        <v>0.3285</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1203</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9912</v>
+        <v>0.6781</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1291</v>
+        <v>0.2136</v>
       </c>
       <c r="P18" t="n">
+        <v>-1.7401</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-2.3926</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.6525</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.2175</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.87</v>
-      </c>
       <c r="S18" t="n">
-        <v>-0.466</v>
+        <v>0.2791</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.399</v>
+        <v>0.2415</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.0375</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6091</v>
+        <v>-1.5705</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4699</v>
+        <v>-2.2464</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8608</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6933</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3442</v>
+        <v>0.3827</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1815</v>
+        <v>0.0421</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5256</v>
+        <v>0.3407</v>
       </c>
       <c r="V19" t="n">
         <v>-1.13</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1684</v>
+        <v>-1.6675</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0242</v>
+        <v>-0.8007</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1442</v>
+        <v>-0.8668</v>
       </c>
       <c r="G20" t="n">
         <v>1.2016</v>
@@ -2014,13 +2014,13 @@
         <v>2.8276</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.6751</v>
+        <v>-2.1742</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2209</v>
+        <v>-0.9974</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.4542</v>
+        <v>-1.1768</v>
       </c>
       <c r="V20" t="n">
         <v>-1.13</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8007</v>
+        <v>-2.5849</v>
       </c>
       <c r="E21" t="n">
         <v>-3.1861</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3854</v>
+        <v>0.6012</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3211</v>
@@ -2092,13 +2092,13 @@
         <v>2.6101</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2621</v>
+        <v>-1.0464</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2019</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0603</v>
+        <v>-0.8445</v>
       </c>
       <c r="V21" t="n">
         <v>1.695</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9618</v>
+        <v>-5.3376</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.4388</v>
+        <v>-5.2153</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.523</v>
+        <v>-0.1223</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4265</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3804</v>
+        <v>-0.7562</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5924</v>
+        <v>-0.3689</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.788</v>
+        <v>-0.3873</v>
       </c>
       <c r="V22" t="n">
         <v>0.7602</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.7964</v>
+        <v>-8.4496</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.3695</v>
+        <v>-6.1459</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.427</v>
+        <v>-2.3037</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5482</v>
@@ -2248,13 +2248,13 @@
         <v>2.6101</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9883</v>
+        <v>-1.6415</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8784</v>
+        <v>-0.6549</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1099</v>
+        <v>-0.9866</v>
       </c>
       <c r="V23" t="n">
         <v>-3.3899</v>
@@ -2284,10 +2284,10 @@
         <v>-11.9726</v>
       </c>
       <c r="E24" t="n">
-        <v>-16.9315</v>
+        <v>-16.9314</v>
       </c>
       <c r="F24" t="n">
-        <v>4.9588</v>
+        <v>4.9589</v>
       </c>
       <c r="G24" t="n">
         <v>-2.992400000000001</v>
@@ -2299,10 +2299,10 @@
         <v>-6.3826</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.8351</v>
+        <v>-2.835099999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>7.0733</v>
+        <v>7.073299999999999</v>
       </c>
       <c r="L24" t="n">
         <v>-9.908899999999999</v>
@@ -2326,13 +2326,13 @@
         <v>21.7506</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.700200000000001</v>
+        <v>-8.7004</v>
       </c>
       <c r="T24" t="n">
         <v>-3.9715</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.728899999999999</v>
+        <v>-4.7289</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4551</v>
